--- a/тестовые_отчёты/тестовые_отчёты/Бухгалтерия_отчёт.xlsx
+++ b/тестовые_отчёты/тестовые_отчёты/Бухгалтерия_отчёт.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Наименование (факт)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Категория (внутр)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Сумма, руб</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Дата операции</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Подразделение</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -471,20 +459,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>часы</t>
+          <t>такси</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>краснухи</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31275</v>
+        <v>18770</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.04.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -504,20 +492,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>офисная бумага</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12600</v>
+        <v>1022</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,20 +525,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>семинары</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>обучение</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1959</v>
+        <v>47501</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04.05.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -579,11 +567,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28149</v>
+        <v>15196</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -612,11 +600,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33032</v>
+        <v>41667</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -626,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -636,20 +624,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>стулья</t>
+          <t>курсы</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32500</v>
+        <v>21669</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.05.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -669,20 +657,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>офисная мебель</t>
+          <t>офисные товары</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37560</v>
+        <v>10072</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.04.2026</t>
+          <t>26.05.2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -692,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -702,20 +690,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>тренинги</t>
+          <t>офисная мебель</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>обучение</t>
+          <t>мебель</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48216</v>
+        <v>24392</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>12.06.2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -725,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -735,20 +723,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>столы</t>
+          <t>такси</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10165</v>
+        <v>28342</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -758,7 +746,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -777,11 +765,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>39708</v>
+        <v>38902</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14.05.2026</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -791,7 +779,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -801,7 +789,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>напитки</t>
+          <t>чай</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -810,11 +798,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>42520</v>
+        <v>34139</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23.04.2026</t>
+          <t>03.06.2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,20 +822,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>салфетки</t>
+          <t>бумага А4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20310</v>
+        <v>12512</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -876,11 +864,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37509</v>
+        <v>42887</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.04.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -900,20 +888,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>столы</t>
+          <t>тренинги</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22207</v>
+        <v>31698</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>28.05.2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -923,7 +911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -933,20 +921,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>курсы</t>
+          <t>бытовая химия</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>обучение</t>
+          <t>хозтовары</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37083</v>
+        <v>40287</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01.05.2026</t>
+          <t>03.06.2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -966,20 +954,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>такси</t>
+          <t>тонер</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25338</v>
+        <v>1343</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>28.05.2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -989,7 +977,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>оплачено</t>
+          <t>ожидает</t>
         </is>
       </c>
     </row>
@@ -999,20 +987,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>курсы</t>
+          <t>расходники принтера</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>обучение</t>
+          <t>картриджи</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37646</v>
+        <v>39354</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.05.2026</t>
+          <t>19.06.2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1032,20 +1020,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>семинары</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7673</v>
+        <v>33365</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.05.2026</t>
+          <t>24.05.2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1065,20 +1053,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>салфетки</t>
+          <t>офисные товары</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>хозтовары</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>49373</v>
+        <v>47572</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1098,20 +1086,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>печенье к чаю</t>
+          <t>тренинги</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>чай_кофе</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24430</v>
+        <v>6627</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>02.06.2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1121,7 +1109,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -1131,20 +1119,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>столы</t>
+          <t>проезд</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>мебель</t>
+          <t>транспорт</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14856</v>
+        <v>49006</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24.04.2026</t>
+          <t>26.05.2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1164,7 +1152,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>печенье к чаю</t>
+          <t>кофе</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1173,11 +1161,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3744</v>
+        <v>6802</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>10.06.2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1187,7 +1175,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -1197,20 +1185,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>чай</t>
+          <t>бытовая химия</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>чай_кофе</t>
+          <t>хозтовары</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25097</v>
+        <v>29557</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>03.05.2026</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1230,20 +1218,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>офисная бумага</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>бумага</t>
+          <t>канцтовары</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19183</v>
+        <v>28453</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30.04.2026</t>
+          <t>27.05.2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1272,11 +1260,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33444</v>
+        <v>42513</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05.05.2026</t>
+          <t>01.06.2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1296,20 +1284,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ГСМ</t>
+          <t>офисная бумага</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>бумага</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49920</v>
+        <v>2238</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.05.2026</t>
+          <t>14.06.2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1319,7 +1307,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
@@ -1329,20 +1317,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>схр</t>
+          <t>семинары</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>краснухи</t>
+          <t>обучение</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1363</v>
+        <v>46163</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29.04.2026</t>
+          <t>05.06.2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1352,106 +1340,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ГСМ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>транспорт</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>49010</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>04.05.2026</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Бухгалтерия</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ожидает</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>часы</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>краснухи</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>18380</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>25.04.2026</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Бухгалтерия</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>оплачено</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>хозтовары</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>хозтовары</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>22836</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>08.05.2026</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Бухгалтерия</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ожидает</t>
+          <t>оплачено</t>
         </is>
       </c>
     </row>
